--- a/server/uploads/Transit-Shipment---Copy.xlsx
+++ b/server/uploads/Transit-Shipment---Copy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Pictures\reports shipment 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FE4A09-90CD-4075-AD31-792A1BD7616A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77C9935-D218-43BF-8B68-35E8A23EB3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <t xml:space="preserve">                            Please review the Example tab before you complete this sheet</t>
   </si>
@@ -241,13 +241,25 @@
   </si>
   <si>
     <t>CRM-CSB5-Black-Red</t>
+  </si>
+  <si>
+    <t>BLR7</t>
+  </si>
+  <si>
+    <t>BLR8</t>
+  </si>
+  <si>
+    <t>BOM5</t>
+  </si>
+  <si>
+    <t>AMD2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -330,6 +342,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -487,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -537,6 +554,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -800,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I886"/>
+  <dimension ref="A1:I889"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -958,8 +978,8 @@
       <c r="B10" s="16">
         <v>16</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>18</v>
+      <c r="C10" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -969,14 +989,14 @@
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9" thickBot="1">
-      <c r="A11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="17">
-        <v>6</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>18</v>
+      <c r="A11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="16">
+        <v>52</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -986,14 +1006,14 @@
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" thickBot="1">
-      <c r="A12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="17">
-        <v>42</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>18</v>
+      <c r="A12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="16">
+        <v>44</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -1003,14 +1023,14 @@
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" thickBot="1">
-      <c r="A13" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="17">
-        <v>15</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>18</v>
+      <c r="A13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="16">
+        <v>46</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -1021,10 +1041,10 @@
     </row>
     <row r="14" spans="1:9" thickBot="1">
       <c r="A14" s="17" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B14" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>18</v>
@@ -1038,10 +1058,10 @@
     </row>
     <row r="15" spans="1:9" thickBot="1">
       <c r="A15" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="17">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>18</v>
@@ -1055,10 +1075,10 @@
     </row>
     <row r="16" spans="1:9" thickBot="1">
       <c r="A16" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>18</v>
@@ -1072,10 +1092,10 @@
     </row>
     <row r="17" spans="1:9" thickBot="1">
       <c r="A17" s="17" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B17" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>18</v>
@@ -1089,10 +1109,10 @@
     </row>
     <row r="18" spans="1:9" thickBot="1">
       <c r="A18" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>18</v>
@@ -1106,10 +1126,10 @@
     </row>
     <row r="19" spans="1:9" thickBot="1">
       <c r="A19" s="17" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B19" s="17">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>18</v>
@@ -1123,10 +1143,10 @@
     </row>
     <row r="20" spans="1:9" thickBot="1">
       <c r="A20" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="17">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>18</v>
@@ -1140,10 +1160,10 @@
     </row>
     <row r="21" spans="1:9" thickBot="1">
       <c r="A21" s="17" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B21" s="17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>18</v>
@@ -1157,10 +1177,10 @@
     </row>
     <row r="22" spans="1:9" thickBot="1">
       <c r="A22" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="17">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>18</v>
@@ -1174,7 +1194,7 @@
     </row>
     <row r="23" spans="1:9" thickBot="1">
       <c r="A23" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="17">
         <v>20</v>
@@ -1191,10 +1211,10 @@
     </row>
     <row r="24" spans="1:9" thickBot="1">
       <c r="A24" s="17" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B24" s="17">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>18</v>
@@ -1208,10 +1228,10 @@
     </row>
     <row r="25" spans="1:9" thickBot="1">
       <c r="A25" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" s="17">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>18</v>
@@ -1225,10 +1245,10 @@
     </row>
     <row r="26" spans="1:9" thickBot="1">
       <c r="A26" s="17" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B26" s="17">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>18</v>
@@ -1242,10 +1262,10 @@
     </row>
     <row r="27" spans="1:9" thickBot="1">
       <c r="A27" s="17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B27" s="17">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>18</v>
@@ -1259,10 +1279,10 @@
     </row>
     <row r="28" spans="1:9" thickBot="1">
       <c r="A28" s="17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B28" s="17">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>18</v>
@@ -1276,10 +1296,10 @@
     </row>
     <row r="29" spans="1:9" thickBot="1">
       <c r="A29" s="17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" s="17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>18</v>
@@ -1293,10 +1313,10 @@
     </row>
     <row r="30" spans="1:9" thickBot="1">
       <c r="A30" s="17" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="17">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>18</v>
@@ -1310,10 +1330,10 @@
     </row>
     <row r="31" spans="1:9" thickBot="1">
       <c r="A31" s="17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" s="17">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>18</v>
@@ -1327,7 +1347,7 @@
     </row>
     <row r="32" spans="1:9" thickBot="1">
       <c r="A32" s="17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B32" s="17">
         <v>10</v>
@@ -1344,7 +1364,7 @@
     </row>
     <row r="33" spans="1:9" thickBot="1">
       <c r="A33" s="17" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B33" s="17">
         <v>10</v>
@@ -1361,10 +1381,10 @@
     </row>
     <row r="34" spans="1:9" thickBot="1">
       <c r="A34" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" s="17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>18</v>
@@ -1378,7 +1398,7 @@
     </row>
     <row r="35" spans="1:9" thickBot="1">
       <c r="A35" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B35" s="17">
         <v>10</v>
@@ -1395,10 +1415,10 @@
     </row>
     <row r="36" spans="1:9" thickBot="1">
       <c r="A36" s="17" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B36" s="17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>18</v>
@@ -1412,10 +1432,10 @@
     </row>
     <row r="37" spans="1:9" thickBot="1">
       <c r="A37" s="17" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="B37" s="17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>18</v>
@@ -1429,10 +1449,10 @@
     </row>
     <row r="38" spans="1:9" thickBot="1">
       <c r="A38" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>18</v>
@@ -1446,10 +1466,10 @@
     </row>
     <row r="39" spans="1:9" thickBot="1">
       <c r="A39" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="17">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>18</v>
@@ -1463,10 +1483,10 @@
     </row>
     <row r="40" spans="1:9" thickBot="1">
       <c r="A40" s="17" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B40" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>18</v>
@@ -1480,7 +1500,7 @@
     </row>
     <row r="41" spans="1:9" thickBot="1">
       <c r="A41" s="17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B41" s="17">
         <v>20</v>
@@ -1497,10 +1517,10 @@
     </row>
     <row r="42" spans="1:9" thickBot="1">
       <c r="A42" s="17" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B42" s="17">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>18</v>
@@ -1514,10 +1534,10 @@
     </row>
     <row r="43" spans="1:9" thickBot="1">
       <c r="A43" s="17" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B43" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>18</v>
@@ -1531,10 +1551,10 @@
     </row>
     <row r="44" spans="1:9" thickBot="1">
       <c r="A44" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>18</v>
@@ -1548,10 +1568,10 @@
     </row>
     <row r="45" spans="1:9" thickBot="1">
       <c r="A45" s="17" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B45" s="17">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>18</v>
@@ -1565,10 +1585,10 @@
     </row>
     <row r="46" spans="1:9" thickBot="1">
       <c r="A46" s="17" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B46" s="17">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>18</v>
@@ -1582,10 +1602,10 @@
     </row>
     <row r="47" spans="1:9" thickBot="1">
       <c r="A47" s="17" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B47" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>18</v>
@@ -1599,10 +1619,10 @@
     </row>
     <row r="48" spans="1:9" thickBot="1">
       <c r="A48" s="17" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B48" s="17">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>18</v>
@@ -1616,10 +1636,10 @@
     </row>
     <row r="49" spans="1:9" thickBot="1">
       <c r="A49" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" s="17">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>18</v>
@@ -1633,10 +1653,10 @@
     </row>
     <row r="50" spans="1:9" thickBot="1">
       <c r="A50" s="17" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B50" s="17">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>18</v>
@@ -1650,10 +1670,10 @@
     </row>
     <row r="51" spans="1:9" thickBot="1">
       <c r="A51" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>18</v>
@@ -1667,10 +1687,10 @@
     </row>
     <row r="52" spans="1:9" thickBot="1">
       <c r="A52" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B52" s="17">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>18</v>
@@ -1684,10 +1704,10 @@
     </row>
     <row r="53" spans="1:9" thickBot="1">
       <c r="A53" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B53" s="17">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>18</v>
@@ -1701,10 +1721,10 @@
     </row>
     <row r="54" spans="1:9" thickBot="1">
       <c r="A54" s="17" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B54" s="17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>18</v>
@@ -1718,10 +1738,10 @@
     </row>
     <row r="55" spans="1:9" thickBot="1">
       <c r="A55" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B55" s="17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>18</v>
@@ -1735,10 +1755,10 @@
     </row>
     <row r="56" spans="1:9" thickBot="1">
       <c r="A56" s="17" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B56" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>18</v>
@@ -1752,10 +1772,10 @@
     </row>
     <row r="57" spans="1:9" thickBot="1">
       <c r="A57" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B57" s="17">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>18</v>
@@ -1767,45 +1787,63 @@
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
     </row>
-    <row r="58" spans="1:9" ht="13.5" thickBot="1">
+    <row r="58" spans="1:9" thickBot="1">
       <c r="A58" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B58" s="17">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" ht="13.5" thickBot="1">
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+    </row>
+    <row r="59" spans="1:9" thickBot="1">
       <c r="A59" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B59" s="17">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" ht="13.5" thickBot="1">
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+    </row>
+    <row r="60" spans="1:9" thickBot="1">
       <c r="A60" s="17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B60" s="17">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
     </row>
     <row r="61" spans="1:9" ht="13.5" thickBot="1">
       <c r="A61" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B61" s="17">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>18</v>
@@ -1813,7 +1851,7 @@
     </row>
     <row r="62" spans="1:9" ht="13.5" thickBot="1">
       <c r="A62" s="17" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B62" s="17">
         <v>30</v>
@@ -1822,31 +1860,49 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15">
-      <c r="A63" s="14" t="s">
+    <row r="63" spans="1:9" ht="13.5" thickBot="1">
+      <c r="A63" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="17">
+        <v>30</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="13.5" thickBot="1">
+      <c r="A64" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B63" s="14">
+      <c r="B64" s="17">
+        <v>30</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A65" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="17">
+        <v>30</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15">
+      <c r="A66" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="14">
         <v>10</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C66" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="15">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-    </row>
-    <row r="65" spans="1:3" ht="15">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-    </row>
-    <row r="66" spans="1:3" ht="15">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
     </row>
     <row r="67" spans="1:3" ht="15">
       <c r="A67" s="14"/>
@@ -2594,18 +2650,18 @@
       <c r="C215" s="14"/>
     </row>
     <row r="216" spans="1:3" ht="15">
-      <c r="A216" s="15"/>
-      <c r="B216" s="15"/>
+      <c r="A216" s="14"/>
+      <c r="B216" s="14"/>
       <c r="C216" s="14"/>
     </row>
     <row r="217" spans="1:3" ht="15">
-      <c r="A217" s="15"/>
-      <c r="B217" s="15"/>
+      <c r="A217" s="14"/>
+      <c r="B217" s="14"/>
       <c r="C217" s="14"/>
     </row>
     <row r="218" spans="1:3" ht="15">
-      <c r="A218" s="15"/>
-      <c r="B218" s="15"/>
+      <c r="A218" s="14"/>
+      <c r="B218" s="14"/>
       <c r="C218" s="14"/>
     </row>
     <row r="219" spans="1:3" ht="15">
@@ -5947,6 +6003,21 @@
       <c r="A886" s="15"/>
       <c r="B886" s="15"/>
       <c r="C886" s="14"/>
+    </row>
+    <row r="887" spans="1:3" ht="15">
+      <c r="A887" s="15"/>
+      <c r="B887" s="15"/>
+      <c r="C887" s="14"/>
+    </row>
+    <row r="888" spans="1:3" ht="15">
+      <c r="A888" s="15"/>
+      <c r="B888" s="15"/>
+      <c r="C888" s="14"/>
+    </row>
+    <row r="889" spans="1:3" ht="15">
+      <c r="A889" s="15"/>
+      <c r="B889" s="15"/>
+      <c r="C889" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5955,6 +6026,7 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A8:C8"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>

--- a/server/uploads/Transit-Shipment---Copy.xlsx
+++ b/server/uploads/Transit-Shipment---Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Pictures\reports shipment 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77C9935-D218-43BF-8B68-35E8A23EB3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C3D32F-1609-4CEF-8E0C-15494E2A49F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t xml:space="preserve">                            Please review the Example tab before you complete this sheet</t>
   </si>
@@ -241,18 +241,6 @@
   </si>
   <si>
     <t>CRM-CSB5-Black-Red</t>
-  </si>
-  <si>
-    <t>BLR7</t>
-  </si>
-  <si>
-    <t>BLR8</t>
-  </si>
-  <si>
-    <t>BOM5</t>
-  </si>
-  <si>
-    <t>AMD2</t>
   </si>
 </sst>
 </file>
@@ -547,6 +535,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -554,9 +545,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -820,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I889"/>
+  <dimension ref="A1:I886"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -873,12 +861,12 @@
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="7"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -888,12 +876,12 @@
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -903,12 +891,12 @@
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -926,11 +914,11 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="16.5">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
@@ -978,73 +966,97 @@
       <c r="B10" s="16">
         <v>16</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>74</v>
+      <c r="C10" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
+      <c r="G10" s="16">
+        <v>630222</v>
+      </c>
+      <c r="H10" s="16">
+        <v>5</v>
+      </c>
+      <c r="I10" s="16">
+        <v>60</v>
+      </c>
     </row>
     <row r="11" spans="1:9" thickBot="1">
-      <c r="A11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="16">
-        <v>52</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>72</v>
+      <c r="A11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="17">
+        <v>6</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
+      <c r="G11" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H11" s="17">
+        <v>5</v>
+      </c>
+      <c r="I11" s="17">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" spans="1:9" thickBot="1">
-      <c r="A12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="16">
-        <v>44</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>73</v>
+      <c r="A12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="17">
+        <v>42</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
+      <c r="G12" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H12" s="17">
+        <v>5</v>
+      </c>
+      <c r="I12" s="17">
+        <v>60</v>
+      </c>
     </row>
     <row r="13" spans="1:9" thickBot="1">
-      <c r="A13" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="16">
-        <v>46</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>75</v>
+      <c r="A13" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="17">
+        <v>15</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
+      <c r="G13" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H13" s="17">
+        <v>5</v>
+      </c>
+      <c r="I13" s="17">
+        <v>120</v>
+      </c>
     </row>
     <row r="14" spans="1:9" thickBot="1">
       <c r="A14" s="17" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B14" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>18</v>
@@ -1052,16 +1064,22 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
+      <c r="G14" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H14" s="17">
+        <v>5</v>
+      </c>
+      <c r="I14" s="17">
+        <v>120</v>
+      </c>
     </row>
     <row r="15" spans="1:9" thickBot="1">
       <c r="A15" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="17">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>18</v>
@@ -1069,16 +1087,22 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
+      <c r="G15" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H15" s="17">
+        <v>5</v>
+      </c>
+      <c r="I15" s="17">
+        <v>120</v>
+      </c>
     </row>
     <row r="16" spans="1:9" thickBot="1">
       <c r="A16" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>18</v>
@@ -1086,16 +1110,22 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
+      <c r="G16" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H16" s="17">
+        <v>5</v>
+      </c>
+      <c r="I16" s="17">
+        <v>180</v>
+      </c>
     </row>
     <row r="17" spans="1:9" thickBot="1">
       <c r="A17" s="17" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B17" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>18</v>
@@ -1103,16 +1133,22 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
+      <c r="G17" s="17">
+        <v>630222</v>
+      </c>
+      <c r="H17" s="17">
+        <v>5</v>
+      </c>
+      <c r="I17" s="17">
+        <v>180</v>
+      </c>
     </row>
     <row r="18" spans="1:9" thickBot="1">
       <c r="A18" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>18</v>
@@ -1120,16 +1156,22 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
+      <c r="G18" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H18" s="17">
+        <v>5</v>
+      </c>
+      <c r="I18" s="17">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" spans="1:9" thickBot="1">
       <c r="A19" s="17" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B19" s="17">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>18</v>
@@ -1137,16 +1179,22 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
+      <c r="G19" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H19" s="17">
+        <v>5</v>
+      </c>
+      <c r="I19" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:9" thickBot="1">
       <c r="A20" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="17">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>18</v>
@@ -1154,16 +1202,22 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
+      <c r="G20" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H20" s="17">
+        <v>5</v>
+      </c>
+      <c r="I20" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:9" thickBot="1">
       <c r="A21" s="17" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B21" s="17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>18</v>
@@ -1171,16 +1225,22 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
+      <c r="G21" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H21" s="17">
+        <v>5</v>
+      </c>
+      <c r="I21" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="22" spans="1:9" thickBot="1">
       <c r="A22" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="17">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>18</v>
@@ -1188,13 +1248,19 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
+      <c r="G22" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H22" s="17">
+        <v>5</v>
+      </c>
+      <c r="I22" s="17">
+        <v>55</v>
+      </c>
     </row>
     <row r="23" spans="1:9" thickBot="1">
       <c r="A23" s="17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B23" s="17">
         <v>20</v>
@@ -1205,16 +1271,22 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
+      <c r="G23" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H23" s="17">
+        <v>5</v>
+      </c>
+      <c r="I23" s="17">
+        <v>30</v>
+      </c>
     </row>
     <row r="24" spans="1:9" thickBot="1">
       <c r="A24" s="17" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="B24" s="17">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>18</v>
@@ -1222,16 +1294,22 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="G24" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H24" s="17">
+        <v>5</v>
+      </c>
+      <c r="I24" s="17">
+        <v>30</v>
+      </c>
     </row>
     <row r="25" spans="1:9" thickBot="1">
       <c r="A25" s="17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" s="17">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>18</v>
@@ -1239,16 +1317,22 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
+      <c r="G25" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H25" s="17">
+        <v>5</v>
+      </c>
+      <c r="I25" s="17">
+        <v>150</v>
+      </c>
     </row>
     <row r="26" spans="1:9" thickBot="1">
       <c r="A26" s="17" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="B26" s="17">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>18</v>
@@ -1256,16 +1340,22 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
+      <c r="G26" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H26" s="17">
+        <v>5</v>
+      </c>
+      <c r="I26" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="27" spans="1:9" thickBot="1">
       <c r="A27" s="17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" s="17">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>18</v>
@@ -1273,16 +1363,22 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
+      <c r="G27" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H27" s="17">
+        <v>5</v>
+      </c>
+      <c r="I27" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="28" spans="1:9" thickBot="1">
       <c r="A28" s="17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" s="17">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>18</v>
@@ -1290,16 +1386,22 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
+      <c r="G28" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H28" s="17">
+        <v>5</v>
+      </c>
+      <c r="I28" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="29" spans="1:9" thickBot="1">
       <c r="A29" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" s="17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>18</v>
@@ -1307,16 +1409,22 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
+      <c r="G29" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H29" s="17">
+        <v>5</v>
+      </c>
+      <c r="I29" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="30" spans="1:9" thickBot="1">
       <c r="A30" s="17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" s="17">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>18</v>
@@ -1324,16 +1432,22 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
+      <c r="G30" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H30" s="17">
+        <v>5</v>
+      </c>
+      <c r="I30" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="31" spans="1:9" thickBot="1">
       <c r="A31" s="17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" s="17">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>18</v>
@@ -1341,13 +1455,19 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
+      <c r="G31" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H31" s="17">
+        <v>5</v>
+      </c>
+      <c r="I31" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="32" spans="1:9" thickBot="1">
       <c r="A32" s="17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" s="17">
         <v>10</v>
@@ -1358,13 +1478,19 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
+      <c r="G32" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H32" s="17">
+        <v>5</v>
+      </c>
+      <c r="I32" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="33" spans="1:9" thickBot="1">
       <c r="A33" s="17" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B33" s="17">
         <v>10</v>
@@ -1375,16 +1501,22 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
+      <c r="G33" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H33" s="17">
+        <v>5</v>
+      </c>
+      <c r="I33" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="34" spans="1:9" thickBot="1">
       <c r="A34" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B34" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>18</v>
@@ -1392,13 +1524,19 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
+      <c r="G34" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H34" s="17">
+        <v>5</v>
+      </c>
+      <c r="I34" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="35" spans="1:9" thickBot="1">
       <c r="A35" s="17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B35" s="17">
         <v>10</v>
@@ -1409,16 +1547,22 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
+      <c r="G35" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H35" s="17">
+        <v>5</v>
+      </c>
+      <c r="I35" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="36" spans="1:9" thickBot="1">
       <c r="A36" s="17" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B36" s="17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>18</v>
@@ -1426,16 +1570,22 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
+      <c r="G36" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H36" s="17">
+        <v>5</v>
+      </c>
+      <c r="I36" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="37" spans="1:9" thickBot="1">
       <c r="A37" s="17" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B37" s="17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>18</v>
@@ -1443,16 +1593,22 @@
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
+      <c r="G37" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H37" s="17">
+        <v>5</v>
+      </c>
+      <c r="I37" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="38" spans="1:9" thickBot="1">
       <c r="A38" s="17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>18</v>
@@ -1460,16 +1616,22 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
+      <c r="G38" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H38" s="17">
+        <v>5</v>
+      </c>
+      <c r="I38" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="39" spans="1:9" thickBot="1">
       <c r="A39" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="17">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>18</v>
@@ -1477,16 +1639,22 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
+      <c r="G39" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H39" s="17">
+        <v>5</v>
+      </c>
+      <c r="I39" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="40" spans="1:9" thickBot="1">
       <c r="A40" s="17" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B40" s="17">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>18</v>
@@ -1494,13 +1662,19 @@
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
+      <c r="G40" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H40" s="17">
+        <v>5</v>
+      </c>
+      <c r="I40" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="41" spans="1:9" thickBot="1">
       <c r="A41" s="17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B41" s="17">
         <v>20</v>
@@ -1511,16 +1685,22 @@
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
+      <c r="G41" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H41" s="17">
+        <v>5</v>
+      </c>
+      <c r="I41" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="42" spans="1:9" thickBot="1">
       <c r="A42" s="17" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B42" s="17">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>18</v>
@@ -1528,16 +1708,22 @@
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
+      <c r="G42" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H42" s="17">
+        <v>5</v>
+      </c>
+      <c r="I42" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="43" spans="1:9" thickBot="1">
       <c r="A43" s="17" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B43" s="17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>18</v>
@@ -1545,16 +1731,22 @@
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
+      <c r="G43" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H43" s="17">
+        <v>5</v>
+      </c>
+      <c r="I43" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="44" spans="1:9" thickBot="1">
       <c r="A44" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" s="17">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>18</v>
@@ -1562,16 +1754,22 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
+      <c r="G44" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H44" s="17">
+        <v>5</v>
+      </c>
+      <c r="I44" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="45" spans="1:9" thickBot="1">
       <c r="A45" s="17" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B45" s="17">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>18</v>
@@ -1579,16 +1777,22 @@
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
+      <c r="G45" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H45" s="17">
+        <v>5</v>
+      </c>
+      <c r="I45" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="46" spans="1:9" thickBot="1">
       <c r="A46" s="17" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B46" s="17">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>18</v>
@@ -1596,16 +1800,22 @@
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
+      <c r="G46" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H46" s="17">
+        <v>5</v>
+      </c>
+      <c r="I46" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="47" spans="1:9" thickBot="1">
       <c r="A47" s="17" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B47" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>18</v>
@@ -1613,16 +1823,22 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
+      <c r="G47" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H47" s="17">
+        <v>5</v>
+      </c>
+      <c r="I47" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="48" spans="1:9" thickBot="1">
       <c r="A48" s="17" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B48" s="17">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>18</v>
@@ -1630,16 +1846,22 @@
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
+      <c r="G48" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H48" s="17">
+        <v>5</v>
+      </c>
+      <c r="I48" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="49" spans="1:9" thickBot="1">
       <c r="A49" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="17">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>18</v>
@@ -1647,16 +1869,22 @@
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
+      <c r="G49" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H49" s="17">
+        <v>5</v>
+      </c>
+      <c r="I49" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="50" spans="1:9" thickBot="1">
       <c r="A50" s="17" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B50" s="17">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>18</v>
@@ -1664,16 +1892,22 @@
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
+      <c r="G50" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H50" s="17">
+        <v>5</v>
+      </c>
+      <c r="I50" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="51" spans="1:9" thickBot="1">
       <c r="A51" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B51" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>18</v>
@@ -1681,16 +1915,22 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
+      <c r="G51" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H51" s="17">
+        <v>5</v>
+      </c>
+      <c r="I51" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="52" spans="1:9" thickBot="1">
       <c r="A52" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B52" s="17">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>18</v>
@@ -1698,16 +1938,22 @@
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
+      <c r="G52" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H52" s="17">
+        <v>5</v>
+      </c>
+      <c r="I52" s="17">
+        <v>300</v>
+      </c>
     </row>
     <row r="53" spans="1:9" thickBot="1">
       <c r="A53" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B53" s="17">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>18</v>
@@ -1715,16 +1961,22 @@
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
+      <c r="G53" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H53" s="17">
+        <v>5</v>
+      </c>
+      <c r="I53" s="17">
+        <v>720</v>
+      </c>
     </row>
     <row r="54" spans="1:9" thickBot="1">
       <c r="A54" s="17" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B54" s="17">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>18</v>
@@ -1732,16 +1984,22 @@
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
+      <c r="G54" s="17">
+        <v>392329</v>
+      </c>
+      <c r="H54" s="17">
+        <v>18</v>
+      </c>
+      <c r="I54" s="17">
+        <v>180</v>
+      </c>
     </row>
     <row r="55" spans="1:9" thickBot="1">
       <c r="A55" s="17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B55" s="17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>18</v>
@@ -1749,16 +2007,22 @@
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
+      <c r="G55" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H55" s="17">
+        <v>5</v>
+      </c>
+      <c r="I55" s="17">
+        <v>180</v>
+      </c>
     </row>
     <row r="56" spans="1:9" thickBot="1">
       <c r="A56" s="17" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B56" s="17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>18</v>
@@ -1766,16 +2030,22 @@
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
+      <c r="G56" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H56" s="17">
+        <v>5</v>
+      </c>
+      <c r="I56" s="17">
+        <v>450</v>
+      </c>
     </row>
     <row r="57" spans="1:9" thickBot="1">
       <c r="A57" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B57" s="17">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>18</v>
@@ -1783,75 +2053,99 @@
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-    </row>
-    <row r="58" spans="1:9" thickBot="1">
+      <c r="G57" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H57" s="17">
+        <v>5</v>
+      </c>
+      <c r="I57" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="13.5" thickBot="1">
       <c r="A58" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B58" s="17">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-    </row>
-    <row r="59" spans="1:9" thickBot="1">
+      <c r="G58" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H58" s="17">
+        <v>5</v>
+      </c>
+      <c r="I58" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="13.5" thickBot="1">
       <c r="A59" s="17" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B59" s="17">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-    </row>
-    <row r="60" spans="1:9" thickBot="1">
+      <c r="G59" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H59" s="17">
+        <v>5</v>
+      </c>
+      <c r="I59" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="13.5" thickBot="1">
       <c r="A60" s="17" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B60" s="17">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
+      <c r="G60" s="17">
+        <v>630790</v>
+      </c>
+      <c r="H60" s="17">
+        <v>5</v>
+      </c>
+      <c r="I60" s="17">
+        <v>40</v>
+      </c>
     </row>
     <row r="61" spans="1:9" ht="13.5" thickBot="1">
       <c r="A61" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B61" s="17">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="G61" s="17">
+        <v>392329</v>
+      </c>
+      <c r="H61" s="17">
+        <v>18</v>
+      </c>
+      <c r="I61" s="17">
+        <v>650</v>
+      </c>
     </row>
     <row r="62" spans="1:9" ht="13.5" thickBot="1">
       <c r="A62" s="17" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B62" s="17">
         <v>30</v>
@@ -1859,50 +2153,41 @@
       <c r="C62" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="13.5" thickBot="1">
-      <c r="A63" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="17">
-        <v>30</v>
-      </c>
-      <c r="C63" s="17" t="s">
+      <c r="G62" s="17">
+        <v>392329</v>
+      </c>
+      <c r="H62" s="17">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="13.5" thickBot="1">
-      <c r="A64" s="17" t="s">
+      <c r="I62" s="17">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15">
+      <c r="A63" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="17">
-        <v>30</v>
-      </c>
-      <c r="C64" s="17" t="s">
+      <c r="B63" s="14">
+        <v>10</v>
+      </c>
+      <c r="C63" s="14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="13.5" thickBot="1">
-      <c r="A65" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="17">
-        <v>30</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>18</v>
-      </c>
+    <row r="64" spans="1:9" ht="15">
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+    </row>
+    <row r="65" spans="1:3" ht="15">
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
     </row>
     <row r="66" spans="1:3" ht="15">
-      <c r="A66" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="14">
-        <v>10</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>18</v>
-      </c>
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
     </row>
     <row r="67" spans="1:3" ht="15">
       <c r="A67" s="14"/>
@@ -2650,18 +2935,18 @@
       <c r="C215" s="14"/>
     </row>
     <row r="216" spans="1:3" ht="15">
-      <c r="A216" s="14"/>
-      <c r="B216" s="14"/>
+      <c r="A216" s="15"/>
+      <c r="B216" s="15"/>
       <c r="C216" s="14"/>
     </row>
     <row r="217" spans="1:3" ht="15">
-      <c r="A217" s="14"/>
-      <c r="B217" s="14"/>
+      <c r="A217" s="15"/>
+      <c r="B217" s="15"/>
       <c r="C217" s="14"/>
     </row>
     <row r="218" spans="1:3" ht="15">
-      <c r="A218" s="14"/>
-      <c r="B218" s="14"/>
+      <c r="A218" s="15"/>
+      <c r="B218" s="15"/>
       <c r="C218" s="14"/>
     </row>
     <row r="219" spans="1:3" ht="15">
@@ -6003,21 +6288,6 @@
       <c r="A886" s="15"/>
       <c r="B886" s="15"/>
       <c r="C886" s="14"/>
-    </row>
-    <row r="887" spans="1:3" ht="15">
-      <c r="A887" s="15"/>
-      <c r="B887" s="15"/>
-      <c r="C887" s="14"/>
-    </row>
-    <row r="888" spans="1:3" ht="15">
-      <c r="A888" s="15"/>
-      <c r="B888" s="15"/>
-      <c r="C888" s="14"/>
-    </row>
-    <row r="889" spans="1:3" ht="15">
-      <c r="A889" s="15"/>
-      <c r="B889" s="15"/>
-      <c r="C889" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
